--- a/AJA/Rohan/Backend/Output/PJPA30_Generated.xlsx
+++ b/AJA/Rohan/Backend/Output/PJPA30_Generated.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="209">
   <si>
     <t xml:space="preserve">Insight ID </t>
   </si>
@@ -94,36 +94,42 @@
     <t>Kumar, Navin</t>
   </si>
   <si>
+    <t>Srivastava, Pramod K.</t>
+  </si>
+  <si>
+    <t>Agarwal, Shashank</t>
+  </si>
+  <si>
     <t>Solanke, Swapnil A.</t>
   </si>
   <si>
-    <t>Srivastava, Pramod K.</t>
-  </si>
-  <si>
-    <t>Agarwal, Shashank</t>
+    <t>Dubey, Rahul K.</t>
   </si>
   <si>
     <t>Gaur, Anil Kumar</t>
   </si>
   <si>
+    <t>Kulkarni, Shubham P.</t>
+  </si>
+  <si>
+    <t>Jain, Dinesh K.</t>
+  </si>
+  <si>
+    <t>Malennavar, Mudiyappa S.</t>
+  </si>
+  <si>
     <t>Parappanavar, Prasad</t>
   </si>
   <si>
-    <t>Kulkarni, Shubham P.</t>
-  </si>
-  <si>
-    <t>Dubey, Rahul K.</t>
-  </si>
-  <si>
-    <t>Jain, Dinesh K.</t>
-  </si>
-  <si>
-    <t>Malennavar, Mudiyappa S.</t>
+    <t>Solanki, Gourishankar</t>
   </si>
   <si>
     <t>Chauhan, Himanshu S.</t>
   </si>
   <si>
+    <t>Rai, Sachin</t>
+  </si>
+  <si>
     <t>Shukla, Prashant</t>
   </si>
   <si>
@@ -133,39 +139,39 @@
     <t>Mishra, Vikas</t>
   </si>
   <si>
-    <t>Solanki, Gourishankar</t>
+    <t>Sharma, Vivek</t>
+  </si>
+  <si>
+    <t>Tripathi, Ravi P.</t>
+  </si>
+  <si>
+    <t>Potu, Anil J.</t>
+  </si>
+  <si>
+    <t>Mishra, Vivek</t>
+  </si>
+  <si>
+    <t>Tandale, Mangesh S.</t>
+  </si>
+  <si>
+    <t>Singh, Subhash</t>
+  </si>
+  <si>
+    <t>Thengil, Gajanan V.</t>
+  </si>
+  <si>
+    <t>Jangir, Ashok K.</t>
+  </si>
+  <si>
+    <t>Kumar, Shivam</t>
   </si>
   <si>
     <t>Pandey, Anmol</t>
   </si>
   <si>
-    <t>Singh, Subhash</t>
-  </si>
-  <si>
-    <t>Thengil, Gajanan V.</t>
-  </si>
-  <si>
-    <t>Kumar, Shivam</t>
-  </si>
-  <si>
-    <t>Jangir, Ashok K.</t>
-  </si>
-  <si>
-    <t>Tandale, Mangesh S.</t>
-  </si>
-  <si>
-    <t>Sharma, Vivek</t>
-  </si>
-  <si>
-    <t>Potu, Anil J.</t>
-  </si>
-  <si>
     <t>Rajnikant, Vaghela</t>
   </si>
   <si>
-    <t>Tripathi, Ravi P.</t>
-  </si>
-  <si>
     <t>5970.0, 5190.0, 6240.0, 5460.0, 6560.0, 5980.0, 6820.0, 5190.0, 5770.0, 4230.0</t>
   </si>
   <si>
@@ -178,36 +184,42 @@
     <t>7680.0, 8272.0, 3864.0, 5630.0, 4896.0, 5698.0, 5966.0, 6532.0</t>
   </si>
   <si>
+    <t>15710.0, 16630.0, 13005.0, 7580.0, 10100.0, 10985.0, 9275.0, 14245.0</t>
+  </si>
+  <si>
+    <t>5842.0, 10722.0, 11144.0, 10896.0, 8530.0, 8952.0, 8840.0, 6902.0</t>
+  </si>
+  <si>
     <t>3240.0, 3508.0, 3430.0, 3566.0, 3410.0, 3550.0, 3308.0, 3990.0</t>
   </si>
   <si>
-    <t>15710.0, 16630.0, 13005.0, 7580.0, 10100.0, 10985.0, 9275.0, 14245.0</t>
-  </si>
-  <si>
-    <t>5842.0, 10722.0, 11144.0, 10896.0, 8530.0, 8952.0, 8840.0, 6902.0</t>
+    <t>3406.0, 3488.0, 3864.0, 5284.0, 5476.0, 3128.0, 3264.0</t>
   </si>
   <si>
     <t>5902.0, 6128.0, 7288.0, 4994.0, 5302.0, 3954.0, 4552.0</t>
   </si>
   <si>
+    <t>3168.0, 3470.0, 3460.0, 3282.0, 3224.0, 3466.0, 3186.0</t>
+  </si>
+  <si>
+    <t>3400.0, 3950.0, 4440.0, 3600.0, 5300.0, 8400.0, 6985.0</t>
+  </si>
+  <si>
+    <t>3060.0, 3202.0, 3318.0, 3024.0, 3034.0, 3192.0, 3048.0</t>
+  </si>
+  <si>
     <t>5338.0, 3190.0, 3282.0, 3054.0, 4102.0, 3962.0, 5676.0</t>
   </si>
   <si>
-    <t>3168.0, 3470.0, 3460.0, 3282.0, 3224.0, 3466.0, 3186.0</t>
-  </si>
-  <si>
-    <t>3406.0, 3488.0, 3864.0, 5284.0, 5476.0, 3128.0, 3264.0</t>
-  </si>
-  <si>
-    <t>3400.0, 3950.0, 4440.0, 3600.0, 5300.0, 8400.0, 6985.0</t>
-  </si>
-  <si>
-    <t>3060.0, 3202.0, 3318.0, 3024.0, 3034.0, 3192.0, 3048.0</t>
+    <t>3080.0, 5230.0, 5910.0, 5115.0, 5150.0, 4240.0</t>
   </si>
   <si>
     <t>3162.0, 7930.0, 6890.0, 5672.0, 4824.0, 4464.0</t>
   </si>
   <si>
+    <t>3038.0, 6112.0, 6080.0, 3014.0, 5374.0, 4194.0</t>
+  </si>
+  <si>
     <t>20860.0, 18740.0, 10350.0, 16710.0, 19650.0, 11500.0</t>
   </si>
   <si>
@@ -217,39 +229,39 @@
     <t>4760.0, 5400.0, 4840.0, 4980.0, 7030.0, 6110.0</t>
   </si>
   <si>
-    <t>3080.0, 5230.0, 5910.0, 5115.0, 5150.0, 4240.0</t>
+    <t>3160.0, 4480.0, 3470.0, 4270.0, 4670.0</t>
+  </si>
+  <si>
+    <t>4700.0, 7410.0, 7380.0, 8710.0, 11010.0</t>
+  </si>
+  <si>
+    <t>3388.0, 3484.0, 3460.0, 3280.0, 3058.0</t>
+  </si>
+  <si>
+    <t>3690.0, 3070.0, 3760.0, 3740.0, 3060.0</t>
+  </si>
+  <si>
+    <t>9600.0, 9515.0, 7830.0, 6170.0, 5020.0</t>
+  </si>
+  <si>
+    <t>3794.0, 5700.0, 4898.0, 3590.0, 3132.0</t>
+  </si>
+  <si>
+    <t>4248.0, 4476.0, 4476.0, 4676.0, 4368.0</t>
+  </si>
+  <si>
+    <t>9450.0, 6470.0, 10580.0, 6530.0, 7220.0</t>
+  </si>
+  <si>
+    <t>15550.0, 12220.0, 11030.0, 14810.0, 5900.0</t>
   </si>
   <si>
     <t>6816.0, 6864.0, 5970.0, 6250.0, 8450.0</t>
   </si>
   <si>
-    <t>3794.0, 5700.0, 4898.0, 3590.0, 3132.0</t>
-  </si>
-  <si>
-    <t>4248.0, 4476.0, 4476.0, 4676.0, 4368.0</t>
-  </si>
-  <si>
-    <t>15550.0, 12220.0, 11030.0, 14810.0, 5900.0</t>
-  </si>
-  <si>
-    <t>9450.0, 6470.0, 10580.0, 6530.0, 7220.0</t>
-  </si>
-  <si>
-    <t>9600.0, 9515.0, 7830.0, 6170.0, 5020.0</t>
-  </si>
-  <si>
-    <t>3160.0, 4480.0, 3470.0, 4270.0, 4670.0</t>
-  </si>
-  <si>
-    <t>3388.0, 3484.0, 3460.0, 3280.0, 3058.0</t>
-  </si>
-  <si>
     <t>6200.0, 3410.0, 4330.0, 6450.0, 4870.0</t>
   </si>
   <si>
-    <t>4700.0, 7410.0, 7380.0, 8710.0, 11010.0</t>
-  </si>
-  <si>
     <t>Market visit</t>
   </si>
   <si>
@@ -259,25 +271,28 @@
     <t>Market Visit</t>
   </si>
   <si>
+    <t>Agra meeting</t>
+  </si>
+  <si>
+    <t>mkt visit for paint and putty</t>
+  </si>
+  <si>
     <t>market visit</t>
   </si>
   <si>
-    <t>Agra meeting</t>
-  </si>
-  <si>
-    <t>mkt visit for paint and putty</t>
-  </si>
-  <si>
     <t>Mobile Expense Claim 2025-04-02</t>
   </si>
   <si>
+    <t>Office Work</t>
+  </si>
+  <si>
+    <t>For Regular Market Visit</t>
+  </si>
+  <si>
     <t>Mobile Expense Claim 2025-02-28</t>
   </si>
   <si>
-    <t>Office Work</t>
-  </si>
-  <si>
-    <t>For Regular Market Visit</t>
+    <t>KAKOO SARUNDA SOBHANA BIKANER</t>
   </si>
   <si>
     <t>oct short visit</t>
@@ -286,21 +301,21 @@
     <t>MARKET VISIT</t>
   </si>
   <si>
-    <t>KAKOO SARUNDA SOBHANA BIKANER</t>
+    <t>Market Expense Report 2025-04-10</t>
+  </si>
+  <si>
+    <t>sausar pandhurna visit</t>
+  </si>
+  <si>
+    <t>Mobile Expense Report 2025-04-02</t>
+  </si>
+  <si>
+    <t>short trip visit</t>
   </si>
   <si>
     <t>Mobile Expense Claim 2025-04-11</t>
   </si>
   <si>
-    <t>short trip visit</t>
-  </si>
-  <si>
-    <t>Mobile Expense Report 2025-04-02</t>
-  </si>
-  <si>
-    <t>Market Expense Report 2025-04-10</t>
-  </si>
-  <si>
     <t>F7989159DAF741F68F7C</t>
   </si>
   <si>
@@ -313,36 +328,42 @@
     <t>DA2FE452B1D94FDFB863</t>
   </si>
   <si>
+    <t>402B31E81E654A069A80</t>
+  </si>
+  <si>
+    <t>74A9B79219044A208B27</t>
+  </si>
+  <si>
     <t>335F81A3F63345AEBD4D</t>
   </si>
   <si>
-    <t>402B31E81E654A069A80</t>
-  </si>
-  <si>
-    <t>74A9B79219044A208B27</t>
+    <t>A0B9443473C64ECA8E57</t>
   </si>
   <si>
     <t>C9DB55EE0B11485ABCE3</t>
   </si>
   <si>
+    <t>13F0B6D5B82A418EA2DD</t>
+  </si>
+  <si>
+    <t>054D51A4F2234F3198C1</t>
+  </si>
+  <si>
+    <t>CDE221E1AC37470B9A9C</t>
+  </si>
+  <si>
     <t>D57583FEC57F47BE9F64</t>
   </si>
   <si>
-    <t>13F0B6D5B82A418EA2DD</t>
-  </si>
-  <si>
-    <t>A0B9443473C64ECA8E57</t>
-  </si>
-  <si>
-    <t>054D51A4F2234F3198C1</t>
-  </si>
-  <si>
-    <t>CDE221E1AC37470B9A9C</t>
+    <t>AC3AA23C9E3D4369861A</t>
   </si>
   <si>
     <t>153FF1C2DD9D45E994E8</t>
   </si>
   <si>
+    <t>CB1AFCB305D44B3B92FF</t>
+  </si>
+  <si>
     <t>3068047C744649C88AAB</t>
   </si>
   <si>
@@ -352,39 +373,39 @@
     <t>7B4CA97873424A29882C</t>
   </si>
   <si>
-    <t>AC3AA23C9E3D4369861A</t>
+    <t>E2766215406341798B8B</t>
+  </si>
+  <si>
+    <t>0C7EDF19FEA74E3FB719</t>
+  </si>
+  <si>
+    <t>B51139F772494B8B8D69</t>
+  </si>
+  <si>
+    <t>285960EB3C2A4D82B75F</t>
+  </si>
+  <si>
+    <t>ABFB3C42AF06427DAA78</t>
+  </si>
+  <si>
+    <t>83D441F642B04D7BA4FE</t>
+  </si>
+  <si>
+    <t>97BE570F588846D1B489</t>
+  </si>
+  <si>
+    <t>26D0E7F9A55A49B383EC</t>
+  </si>
+  <si>
+    <t>E0F9B5AE36ED45DEAD6F</t>
   </si>
   <si>
     <t>F7F2202324E243089A91</t>
   </si>
   <si>
-    <t>83D441F642B04D7BA4FE</t>
-  </si>
-  <si>
-    <t>97BE570F588846D1B489</t>
-  </si>
-  <si>
-    <t>E0F9B5AE36ED45DEAD6F</t>
-  </si>
-  <si>
-    <t>26D0E7F9A55A49B383EC</t>
-  </si>
-  <si>
-    <t>ABFB3C42AF06427DAA78</t>
-  </si>
-  <si>
-    <t>E2766215406341798B8B</t>
-  </si>
-  <si>
-    <t>B51139F772494B8B8D69</t>
-  </si>
-  <si>
     <t>60E77A668FA0481E94FD</t>
   </si>
   <si>
-    <t>0C7EDF19FEA74E3FB719</t>
-  </si>
-  <si>
     <t>KEDU6S</t>
   </si>
   <si>
@@ -397,36 +418,42 @@
     <t>AZ84FU</t>
   </si>
   <si>
+    <t>QLW1T4</t>
+  </si>
+  <si>
+    <t>JGE0XM</t>
+  </si>
+  <si>
     <t>ROBAVG</t>
   </si>
   <si>
-    <t>QLW1T4</t>
-  </si>
-  <si>
-    <t>JGE0XM</t>
+    <t>GEPAX6</t>
   </si>
   <si>
     <t>GL45HK</t>
   </si>
   <si>
+    <t>OVNPDK</t>
+  </si>
+  <si>
+    <t>XGNV2O</t>
+  </si>
+  <si>
+    <t>QHHQA3</t>
+  </si>
+  <si>
     <t>KYXW0N</t>
   </si>
   <si>
-    <t>OVNPDK</t>
-  </si>
-  <si>
-    <t>GEPAX6</t>
-  </si>
-  <si>
-    <t>XGNV2O</t>
-  </si>
-  <si>
-    <t>QHHQA3</t>
+    <t>0GYFYR</t>
   </si>
   <si>
     <t>H14SIX</t>
   </si>
   <si>
+    <t>CALA3Z</t>
+  </si>
+  <si>
     <t>U7A9OP</t>
   </si>
   <si>
@@ -436,39 +463,39 @@
     <t>550FT4</t>
   </si>
   <si>
-    <t>0GYFYR</t>
+    <t>JM40JW</t>
+  </si>
+  <si>
+    <t>EZBF5G</t>
+  </si>
+  <si>
+    <t>FZQDGT</t>
+  </si>
+  <si>
+    <t>1QA3UH</t>
+  </si>
+  <si>
+    <t>ZLBQXM</t>
+  </si>
+  <si>
+    <t>NQGMGO</t>
+  </si>
+  <si>
+    <t>YL3PAF</t>
+  </si>
+  <si>
+    <t>BWST3B</t>
+  </si>
+  <si>
+    <t>96YISD</t>
   </si>
   <si>
     <t>GWK4MF</t>
   </si>
   <si>
-    <t>NQGMGO</t>
-  </si>
-  <si>
-    <t>YL3PAF</t>
-  </si>
-  <si>
-    <t>96YISD</t>
-  </si>
-  <si>
-    <t>BWST3B</t>
-  </si>
-  <si>
-    <t>ZLBQXM</t>
-  </si>
-  <si>
-    <t>JM40JW</t>
-  </si>
-  <si>
-    <t>FZQDGT</t>
-  </si>
-  <si>
     <t>GHEVMP</t>
   </si>
   <si>
-    <t>EZBF5G</t>
-  </si>
-  <si>
     <t>2025-03-31T06:41:01.183</t>
   </si>
   <si>
@@ -481,36 +508,42 @@
     <t>2025-03-31T11:07:56.069</t>
   </si>
   <si>
+    <t>2025-04-04T11:06:25.117</t>
+  </si>
+  <si>
+    <t>2025-03-31T12:22:01.523</t>
+  </si>
+  <si>
     <t>2025-04-08T09:42:14.043</t>
   </si>
   <si>
-    <t>2025-04-04T11:06:25.117</t>
-  </si>
-  <si>
-    <t>2025-03-31T12:22:01.523</t>
+    <t>2025-04-13T14:01:08.001</t>
   </si>
   <si>
     <t>2025-04-02T11:45:10.917</t>
   </si>
   <si>
+    <t>2025-04-06T14:29:06.617</t>
+  </si>
+  <si>
+    <t>2025-03-31T12:01:49.247</t>
+  </si>
+  <si>
+    <t>2025-04-03T10:27:18.643</t>
+  </si>
+  <si>
     <t>2025-03-31T12:23:56.082</t>
   </si>
   <si>
-    <t>2025-04-06T14:29:06.617</t>
-  </si>
-  <si>
-    <t>2025-04-13T14:01:08.001</t>
-  </si>
-  <si>
-    <t>2025-03-31T12:01:49.247</t>
-  </si>
-  <si>
-    <t>2025-04-03T10:27:18.643</t>
+    <t>2025-04-07T10:31:26.047</t>
   </si>
   <si>
     <t>2025-04-04T05:23:08.307</t>
   </si>
   <si>
+    <t>2025-03-31T10:26:13.723</t>
+  </si>
+  <si>
     <t>2025-03-31T04:02:45.008</t>
   </si>
   <si>
@@ -520,39 +553,39 @@
     <t>2025-04-03T14:16:56.897</t>
   </si>
   <si>
-    <t>2025-04-07T10:31:26.047</t>
+    <t>2025-04-10T14:33:37.947</t>
+  </si>
+  <si>
+    <t>2025-04-08T07:36:34.927</t>
+  </si>
+  <si>
+    <t>2025-04-06T01:00:51.044</t>
+  </si>
+  <si>
+    <t>2025-09-09T13:43:33.277</t>
+  </si>
+  <si>
+    <t>2025-04-11T04:13:58.019</t>
+  </si>
+  <si>
+    <t>2025-04-06T10:40:18.853</t>
+  </si>
+  <si>
+    <t>2025-04-07T02:12:54.557</t>
+  </si>
+  <si>
+    <t>2025-04-12T11:37:26.567</t>
+  </si>
+  <si>
+    <t>2025-04-05T02:30:17.127</t>
   </si>
   <si>
     <t>2025-04-14T01:12:38.473</t>
   </si>
   <si>
-    <t>2025-04-06T10:40:18.853</t>
-  </si>
-  <si>
-    <t>2025-04-07T02:12:54.557</t>
-  </si>
-  <si>
-    <t>2025-04-05T02:30:17.127</t>
-  </si>
-  <si>
-    <t>2025-04-12T11:37:26.567</t>
-  </si>
-  <si>
-    <t>2025-04-11T04:13:58.019</t>
-  </si>
-  <si>
-    <t>2025-04-10T14:33:37.947</t>
-  </si>
-  <si>
-    <t>2025-04-06T01:00:51.044</t>
-  </si>
-  <si>
     <t>2025-04-11T01:58:03.887</t>
   </si>
   <si>
-    <t>2025-04-08T07:36:34.927</t>
-  </si>
-  <si>
     <t>Approved</t>
   </si>
   <si>
@@ -565,10 +598,13 @@
     <t>2025-04-10T00:00</t>
   </si>
   <si>
+    <t>2025-04-04T00:00</t>
+  </si>
+  <si>
     <t>2025-02-22T00:00</t>
   </si>
   <si>
-    <t>2025-04-04T00:00</t>
+    <t>2025-04-13T00:00</t>
   </si>
   <si>
     <t>2025-04-02T00:00</t>
@@ -577,12 +613,12 @@
     <t>2025-04-06T00:00</t>
   </si>
   <si>
-    <t>2025-04-13T00:00</t>
-  </si>
-  <si>
     <t>2025-03-01T00:00</t>
   </si>
   <si>
+    <t>2025-04-07T00:00</t>
+  </si>
+  <si>
     <t>2025-03-30T00:00</t>
   </si>
   <si>
@@ -592,16 +628,16 @@
     <t>2025-04-03T00:00</t>
   </si>
   <si>
-    <t>2025-04-07T00:00</t>
+    <t>2025-04-08T00:00</t>
+  </si>
+  <si>
+    <t>2025-09-09T00:00</t>
+  </si>
+  <si>
+    <t>2025-04-12T00:00</t>
   </si>
   <si>
     <t>2025-04-11T00:00</t>
-  </si>
-  <si>
-    <t>2025-04-12T00:00</t>
-  </si>
-  <si>
-    <t>2025-04-08T00:00</t>
   </si>
   <si>
     <t>Short trip</t>
@@ -940,7 +976,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P33"/>
+  <dimension ref="A1:P35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1028,28 +1064,28 @@
         <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E6">
         <v>57410</v>
       </c>
       <c r="F6" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G6" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="H6" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="I6" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="J6" t="s">
         <v>22</v>
       </c>
       <c r="K6" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="L6" s="1">
         <v>45733</v>
@@ -1058,10 +1094,10 @@
         <v>45733</v>
       </c>
       <c r="N6" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="O6" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="P6">
         <v>5970</v>
@@ -1078,28 +1114,28 @@
         <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E7">
         <v>59269.6</v>
       </c>
       <c r="F7" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G7" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="H7" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="I7" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="J7" t="s">
         <v>23</v>
       </c>
       <c r="K7" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="L7" s="1">
         <v>45748</v>
@@ -1108,10 +1144,10 @@
         <v>45748</v>
       </c>
       <c r="N7" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="O7" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="P7">
         <v>6519.6</v>
@@ -1128,28 +1164,28 @@
         <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E8">
         <v>33960</v>
       </c>
       <c r="F8" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G8" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="H8" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="I8" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="J8" t="s">
         <v>24</v>
       </c>
       <c r="K8" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="L8" s="1">
         <v>45742</v>
@@ -1158,10 +1194,10 @@
         <v>45742</v>
       </c>
       <c r="N8" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="O8" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="P8">
         <v>3580</v>
@@ -1178,28 +1214,28 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E9">
         <v>48538</v>
       </c>
       <c r="F9" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G9" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="H9" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="I9" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="J9" t="s">
         <v>25</v>
       </c>
       <c r="K9" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="L9" s="1">
         <v>45747</v>
@@ -1208,10 +1244,10 @@
         <v>45747</v>
       </c>
       <c r="N9" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="O9" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="P9">
         <v>7680</v>
@@ -1222,49 +1258,49 @@
         <v>26</v>
       </c>
       <c r="B10">
-        <v>13003144</v>
+        <v>13000271</v>
       </c>
       <c r="C10">
         <v>8</v>
       </c>
       <c r="D10" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E10">
-        <v>28002</v>
+        <v>97530</v>
       </c>
       <c r="F10" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G10" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H10" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="I10" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="J10" t="s">
         <v>26</v>
       </c>
       <c r="K10" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="L10" s="1">
-        <v>45614</v>
+        <v>45589</v>
       </c>
       <c r="M10" s="1">
-        <v>45614</v>
+        <v>45589</v>
       </c>
       <c r="N10" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="O10" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="P10">
-        <v>3240</v>
+        <v>15710</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1272,49 +1308,49 @@
         <v>27</v>
       </c>
       <c r="B11">
-        <v>13000271</v>
+        <v>13002286</v>
       </c>
       <c r="C11">
         <v>8</v>
       </c>
       <c r="D11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E11">
-        <v>97530</v>
+        <v>71828</v>
       </c>
       <c r="F11" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G11" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="H11" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="I11" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="J11" t="s">
         <v>27</v>
       </c>
       <c r="K11" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="L11" s="1">
-        <v>45589</v>
+        <v>45536</v>
       </c>
       <c r="M11" s="1">
-        <v>45589</v>
+        <v>45536</v>
       </c>
       <c r="N11" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="O11" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="P11">
-        <v>15710</v>
+        <v>5842</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1322,49 +1358,49 @@
         <v>28</v>
       </c>
       <c r="B12">
-        <v>13002286</v>
+        <v>13003144</v>
       </c>
       <c r="C12">
         <v>8</v>
       </c>
       <c r="D12" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E12">
-        <v>71828</v>
+        <v>28002</v>
       </c>
       <c r="F12" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="G12" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="H12" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="I12" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="J12" t="s">
         <v>28</v>
       </c>
       <c r="K12" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="L12" s="1">
-        <v>45536</v>
+        <v>45614</v>
       </c>
       <c r="M12" s="1">
-        <v>45536</v>
+        <v>45614</v>
       </c>
       <c r="N12" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="O12" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="P12">
-        <v>5842</v>
+        <v>3240</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1372,49 +1408,49 @@
         <v>29</v>
       </c>
       <c r="B13">
-        <v>13004092</v>
+        <v>13004073</v>
       </c>
       <c r="C13">
         <v>7</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E13">
-        <v>38120</v>
+        <v>27910</v>
       </c>
       <c r="F13" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G13" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="H13" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="I13" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="J13" t="s">
         <v>29</v>
       </c>
       <c r="K13" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="L13" s="1">
-        <v>45749</v>
+        <v>45761</v>
       </c>
       <c r="M13" s="1">
-        <v>45749</v>
+        <v>45761</v>
       </c>
       <c r="N13" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="O13" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="P13">
-        <v>5902</v>
+        <v>3406</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -1422,49 +1458,49 @@
         <v>30</v>
       </c>
       <c r="B14">
-        <v>13003883</v>
+        <v>13004092</v>
       </c>
       <c r="C14">
         <v>7</v>
       </c>
       <c r="D14" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E14">
-        <v>28604</v>
+        <v>38120</v>
       </c>
       <c r="F14" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G14" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="H14" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="I14" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="J14" t="s">
         <v>30</v>
       </c>
       <c r="K14" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="L14" s="1">
-        <v>45716</v>
+        <v>45749</v>
       </c>
       <c r="M14" s="1">
-        <v>45716</v>
+        <v>45749</v>
       </c>
       <c r="N14" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="O14" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="P14">
-        <v>5338</v>
+        <v>5902</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -1478,28 +1514,28 @@
         <v>7</v>
       </c>
       <c r="D15" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E15">
         <v>23256</v>
       </c>
       <c r="F15" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G15" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="H15" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="I15" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="J15" t="s">
         <v>31</v>
       </c>
       <c r="K15" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="L15" s="1">
         <v>45710</v>
@@ -1508,10 +1544,10 @@
         <v>45710</v>
       </c>
       <c r="N15" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="O15" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="P15">
         <v>3168</v>
@@ -1522,49 +1558,49 @@
         <v>32</v>
       </c>
       <c r="B16">
-        <v>13004073</v>
+        <v>13004367</v>
       </c>
       <c r="C16">
         <v>7</v>
       </c>
       <c r="D16" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E16">
-        <v>27910</v>
+        <v>36075</v>
       </c>
       <c r="F16" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G16" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="H16" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="I16" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="J16" t="s">
         <v>32</v>
       </c>
       <c r="K16" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="L16" s="1">
-        <v>45761</v>
+        <v>45747</v>
       </c>
       <c r="M16" s="1">
-        <v>45761</v>
+        <v>45747</v>
       </c>
       <c r="N16" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="O16" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="P16">
-        <v>3406</v>
+        <v>3400</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -1572,49 +1608,49 @@
         <v>33</v>
       </c>
       <c r="B17">
-        <v>13004367</v>
+        <v>13002027</v>
       </c>
       <c r="C17">
         <v>7</v>
       </c>
       <c r="D17" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E17">
-        <v>36075</v>
+        <v>21878</v>
       </c>
       <c r="F17" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G17" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H17" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="I17" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="J17" t="s">
         <v>33</v>
       </c>
       <c r="K17" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="L17" s="1">
-        <v>45747</v>
+        <v>45712</v>
       </c>
       <c r="M17" s="1">
-        <v>45747</v>
+        <v>45712</v>
       </c>
       <c r="N17" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="O17" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="P17">
-        <v>3400</v>
+        <v>3060</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -1622,49 +1658,49 @@
         <v>34</v>
       </c>
       <c r="B18">
-        <v>13002027</v>
+        <v>13003883</v>
       </c>
       <c r="C18">
         <v>7</v>
       </c>
       <c r="D18" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E18">
-        <v>21878</v>
+        <v>28604</v>
       </c>
       <c r="F18" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="G18" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="H18" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="I18" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="J18" t="s">
         <v>34</v>
       </c>
       <c r="K18" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="L18" s="1">
-        <v>45712</v>
+        <v>45716</v>
       </c>
       <c r="M18" s="1">
-        <v>45712</v>
+        <v>45716</v>
       </c>
       <c r="N18" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="O18" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="P18">
-        <v>3060</v>
+        <v>5338</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -1672,49 +1708,49 @@
         <v>35</v>
       </c>
       <c r="B19">
-        <v>13005508</v>
+        <v>13005125</v>
       </c>
       <c r="C19">
         <v>6</v>
       </c>
       <c r="D19" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E19">
-        <v>32942</v>
+        <v>28725</v>
       </c>
       <c r="F19" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="G19" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="H19" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="I19" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="J19" t="s">
         <v>35</v>
       </c>
       <c r="K19" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="L19" s="1">
-        <v>45684</v>
+        <v>45754</v>
       </c>
       <c r="M19" s="1">
-        <v>45684</v>
+        <v>45754</v>
       </c>
       <c r="N19" t="s">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="O19" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="P19">
-        <v>3162</v>
+        <v>3080</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -1722,49 +1758,49 @@
         <v>36</v>
       </c>
       <c r="B20">
-        <v>13001636</v>
+        <v>13005508</v>
       </c>
       <c r="C20">
         <v>6</v>
       </c>
       <c r="D20" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E20">
-        <v>97810</v>
+        <v>32942</v>
       </c>
       <c r="F20" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G20" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="H20" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="I20" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="J20" t="s">
         <v>36</v>
       </c>
       <c r="K20" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="L20" s="1">
-        <v>45566</v>
+        <v>45684</v>
       </c>
       <c r="M20" s="1">
-        <v>45566</v>
+        <v>45684</v>
       </c>
       <c r="N20" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="O20" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="P20">
-        <v>20860</v>
+        <v>3162</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -1772,49 +1808,49 @@
         <v>37</v>
       </c>
       <c r="B21">
-        <v>13002949</v>
+        <v>13005884</v>
       </c>
       <c r="C21">
         <v>6</v>
       </c>
       <c r="D21" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E21">
-        <v>26660</v>
+        <v>27812</v>
       </c>
       <c r="F21" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G21" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="H21" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="I21" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="J21" t="s">
         <v>37</v>
       </c>
       <c r="K21" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="L21" s="1">
-        <v>45748</v>
+        <v>45743</v>
       </c>
       <c r="M21" s="1">
-        <v>45748</v>
+        <v>45743</v>
       </c>
       <c r="N21" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O21" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="P21">
-        <v>4770</v>
+        <v>3038</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -1822,49 +1858,49 @@
         <v>38</v>
       </c>
       <c r="B22">
-        <v>13002669</v>
+        <v>13001636</v>
       </c>
       <c r="C22">
         <v>6</v>
       </c>
       <c r="D22" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E22">
-        <v>33120</v>
+        <v>97810</v>
       </c>
       <c r="F22" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="G22" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="H22" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="I22" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="J22" t="s">
         <v>38</v>
       </c>
       <c r="K22" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="L22" s="1">
-        <v>45741</v>
+        <v>45566</v>
       </c>
       <c r="M22" s="1">
-        <v>45741</v>
+        <v>45566</v>
       </c>
       <c r="N22" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="O22" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="P22">
-        <v>4760</v>
+        <v>20860</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -1872,49 +1908,49 @@
         <v>39</v>
       </c>
       <c r="B23">
-        <v>13005125</v>
+        <v>13002949</v>
       </c>
       <c r="C23">
         <v>6</v>
       </c>
       <c r="D23" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E23">
-        <v>28725</v>
+        <v>26660</v>
       </c>
       <c r="F23" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="G23" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="H23" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="I23" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="J23" t="s">
         <v>39</v>
       </c>
       <c r="K23" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="L23" s="1">
-        <v>45754</v>
+        <v>45748</v>
       </c>
       <c r="M23" s="1">
-        <v>45754</v>
+        <v>45748</v>
       </c>
       <c r="N23" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="O23" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="P23">
-        <v>3080</v>
+        <v>4770</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -1922,49 +1958,49 @@
         <v>40</v>
       </c>
       <c r="B24">
-        <v>13004733</v>
+        <v>13002669</v>
       </c>
       <c r="C24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D24" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E24">
-        <v>34350</v>
+        <v>33120</v>
       </c>
       <c r="F24" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G24" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="H24" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="I24" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="J24" t="s">
         <v>40</v>
       </c>
       <c r="K24" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="L24" s="1">
-        <v>45758</v>
+        <v>45741</v>
       </c>
       <c r="M24" s="1">
-        <v>45758</v>
+        <v>45741</v>
       </c>
       <c r="N24" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="O24" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="P24">
-        <v>6816</v>
+        <v>4760</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -1972,49 +2008,49 @@
         <v>41</v>
       </c>
       <c r="B25">
-        <v>13005325</v>
+        <v>13003583</v>
       </c>
       <c r="C25">
         <v>5</v>
       </c>
       <c r="D25" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E25">
-        <v>21114</v>
+        <v>20050</v>
       </c>
       <c r="F25" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="G25" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="H25" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="I25" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="J25" t="s">
         <v>41</v>
       </c>
       <c r="K25" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="L25" s="1">
-        <v>45719</v>
+        <v>45758</v>
       </c>
       <c r="M25" s="1">
-        <v>45719</v>
+        <v>45758</v>
       </c>
       <c r="N25" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="O25" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="P25">
-        <v>3794</v>
+        <v>3160</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2022,49 +2058,49 @@
         <v>42</v>
       </c>
       <c r="B26">
-        <v>13004210</v>
+        <v>13005707</v>
       </c>
       <c r="C26">
         <v>5</v>
       </c>
       <c r="D26" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E26">
-        <v>22244</v>
+        <v>39210</v>
       </c>
       <c r="F26" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="G26" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="H26" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="I26" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="J26" t="s">
         <v>42</v>
       </c>
       <c r="K26" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="L26" s="1">
-        <v>45748</v>
+        <v>45741</v>
       </c>
       <c r="M26" s="1">
-        <v>45748</v>
+        <v>45741</v>
       </c>
       <c r="N26" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="O26" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="P26">
-        <v>4248</v>
+        <v>4700</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2072,49 +2108,49 @@
         <v>43</v>
       </c>
       <c r="B27">
-        <v>13002575</v>
+        <v>13005491</v>
       </c>
       <c r="C27">
         <v>5</v>
       </c>
       <c r="D27" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E27">
-        <v>59510</v>
+        <v>16670</v>
       </c>
       <c r="F27" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="G27" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="H27" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="I27" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="J27" t="s">
         <v>43</v>
       </c>
       <c r="K27" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="L27" s="1">
-        <v>45745</v>
+        <v>45714</v>
       </c>
       <c r="M27" s="1">
-        <v>45745</v>
+        <v>45714</v>
       </c>
       <c r="N27" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="O27" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="P27">
-        <v>15550</v>
+        <v>3388</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2122,49 +2158,49 @@
         <v>44</v>
       </c>
       <c r="B28">
-        <v>13005500</v>
+        <v>13002527</v>
       </c>
       <c r="C28">
         <v>5</v>
       </c>
       <c r="D28" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E28">
-        <v>40250</v>
+        <v>17320</v>
       </c>
       <c r="F28" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="G28" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="H28" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="I28" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="J28" t="s">
         <v>44</v>
       </c>
       <c r="K28" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="L28" s="1">
-        <v>45759</v>
+        <v>45902</v>
       </c>
       <c r="M28" s="1">
-        <v>45759</v>
+        <v>45902</v>
       </c>
       <c r="N28" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="O28" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="P28">
-        <v>9450</v>
+        <v>3690</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2178,28 +2214,28 @@
         <v>5</v>
       </c>
       <c r="D29" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E29">
         <v>38135</v>
       </c>
       <c r="F29" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="G29" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="H29" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I29" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="J29" t="s">
         <v>45</v>
       </c>
       <c r="K29" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="L29" s="1">
         <v>45749</v>
@@ -2208,10 +2244,10 @@
         <v>45749</v>
       </c>
       <c r="N29" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="O29" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="P29">
         <v>9600</v>
@@ -2222,49 +2258,49 @@
         <v>46</v>
       </c>
       <c r="B30">
-        <v>13003583</v>
+        <v>13005325</v>
       </c>
       <c r="C30">
         <v>5</v>
       </c>
       <c r="D30" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E30">
-        <v>20050</v>
+        <v>21114</v>
       </c>
       <c r="F30" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="G30" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="H30" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="I30" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="J30" t="s">
         <v>46</v>
       </c>
       <c r="K30" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="L30" s="1">
-        <v>45758</v>
+        <v>45719</v>
       </c>
       <c r="M30" s="1">
-        <v>45758</v>
+        <v>45719</v>
       </c>
       <c r="N30" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="O30" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="P30">
-        <v>3160</v>
+        <v>3794</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2272,49 +2308,49 @@
         <v>47</v>
       </c>
       <c r="B31">
-        <v>13005491</v>
+        <v>13004210</v>
       </c>
       <c r="C31">
         <v>5</v>
       </c>
       <c r="D31" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E31">
-        <v>16670</v>
+        <v>22244</v>
       </c>
       <c r="F31" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="G31" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="H31" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="I31" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="J31" t="s">
         <v>47</v>
       </c>
       <c r="K31" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="L31" s="1">
-        <v>45714</v>
+        <v>45748</v>
       </c>
       <c r="M31" s="1">
-        <v>45714</v>
+        <v>45748</v>
       </c>
       <c r="N31" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="O31" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="P31">
-        <v>3388</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -2322,49 +2358,49 @@
         <v>48</v>
       </c>
       <c r="B32">
-        <v>13004729</v>
+        <v>13005500</v>
       </c>
       <c r="C32">
         <v>5</v>
       </c>
       <c r="D32" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E32">
-        <v>25260</v>
+        <v>40250</v>
       </c>
       <c r="F32" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G32" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="H32" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="I32" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="J32" t="s">
         <v>48</v>
       </c>
       <c r="K32" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="L32" s="1">
-        <v>45758</v>
+        <v>45759</v>
       </c>
       <c r="M32" s="1">
-        <v>45758</v>
+        <v>45759</v>
       </c>
       <c r="N32" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="O32" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="P32">
-        <v>6200</v>
+        <v>9450</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -2372,49 +2408,149 @@
         <v>49</v>
       </c>
       <c r="B33">
-        <v>13005707</v>
+        <v>13002575</v>
       </c>
       <c r="C33">
         <v>5</v>
       </c>
       <c r="D33" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E33">
-        <v>39210</v>
+        <v>59510</v>
       </c>
       <c r="F33" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G33" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="H33" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="I33" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="J33" t="s">
         <v>49</v>
       </c>
       <c r="K33" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="L33" s="1">
-        <v>45741</v>
+        <v>45745</v>
       </c>
       <c r="M33" s="1">
-        <v>45741</v>
+        <v>45745</v>
       </c>
       <c r="N33" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="O33" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="P33">
-        <v>4700</v>
+        <v>15550</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16">
+      <c r="A34" t="s">
+        <v>50</v>
+      </c>
+      <c r="B34">
+        <v>13004733</v>
+      </c>
+      <c r="C34">
+        <v>5</v>
+      </c>
+      <c r="D34" t="s">
+        <v>80</v>
+      </c>
+      <c r="E34">
+        <v>34350</v>
+      </c>
+      <c r="F34" t="s">
+        <v>99</v>
+      </c>
+      <c r="G34" t="s">
+        <v>128</v>
+      </c>
+      <c r="H34" t="s">
+        <v>158</v>
+      </c>
+      <c r="I34" t="s">
+        <v>188</v>
+      </c>
+      <c r="J34" t="s">
+        <v>50</v>
+      </c>
+      <c r="K34" t="s">
+        <v>190</v>
+      </c>
+      <c r="L34" s="1">
+        <v>45758</v>
+      </c>
+      <c r="M34" s="1">
+        <v>45758</v>
+      </c>
+      <c r="N34" t="s">
+        <v>207</v>
+      </c>
+      <c r="O34" t="s">
+        <v>208</v>
+      </c>
+      <c r="P34">
+        <v>6816</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16">
+      <c r="A35" t="s">
+        <v>51</v>
+      </c>
+      <c r="B35">
+        <v>13004729</v>
+      </c>
+      <c r="C35">
+        <v>5</v>
+      </c>
+      <c r="D35" t="s">
+        <v>81</v>
+      </c>
+      <c r="E35">
+        <v>25260</v>
+      </c>
+      <c r="F35" t="s">
+        <v>87</v>
+      </c>
+      <c r="G35" t="s">
+        <v>129</v>
+      </c>
+      <c r="H35" t="s">
+        <v>159</v>
+      </c>
+      <c r="I35" t="s">
+        <v>189</v>
+      </c>
+      <c r="J35" t="s">
+        <v>51</v>
+      </c>
+      <c r="K35" t="s">
+        <v>190</v>
+      </c>
+      <c r="L35" s="1">
+        <v>45758</v>
+      </c>
+      <c r="M35" s="1">
+        <v>45758</v>
+      </c>
+      <c r="N35" t="s">
+        <v>207</v>
+      </c>
+      <c r="O35" t="s">
+        <v>208</v>
+      </c>
+      <c r="P35">
+        <v>6200</v>
       </c>
     </row>
   </sheetData>
